--- a/output/pdf_financials_xlsx/BEAR.xlsx
+++ b/output/pdf_financials_xlsx/BEAR.xlsx
@@ -4889,34 +4889,34 @@
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.340548</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.402381</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.402381</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.387256</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.3035</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.014079</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.014079</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.014079</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.014079</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.014079</v>
       </c>
     </row>
     <row r="93">
@@ -7811,7 +7811,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -9128,7 +9132,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -9754,7 +9762,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BEAR.xlsx
+++ b/output/pdf_financials_xlsx/BEAR.xlsx
@@ -954,7 +954,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.011698</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1746,7 +1746,7 @@
         <v>-0.405712</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.06816899999999999</v>
+        <v>-0.07986699999999999</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.19112</v>
@@ -1842,7 +1842,7 @@
         <v>-0.405054</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.067638</v>
+        <v>-0.079336</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.190689</v>
@@ -2060,43 +2060,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.033974</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.496923</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.180935</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.06529600000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.083038</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.05695</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.034105</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.028006</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.130853</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.034141</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.065483</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.004595</v>
       </c>
     </row>
     <row r="35">
@@ -2152,43 +2152,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.033974</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.496923</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.180935</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.06529600000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.083038</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.05695</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.034105</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.028006</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.130853</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.034141</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.065483</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.004595</v>
       </c>
     </row>
     <row r="37">
@@ -2704,43 +2704,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.034556</v>
+        <v>0.0005820000000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.540767</v>
+        <v>0.043844</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.284657</v>
+        <v>0.103722</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.075822</v>
+        <v>0.010526</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.163322</v>
+        <v>0.08028399999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.05695</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.086725</v>
+        <v>0.05262</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.033006</v>
+        <v>0.005</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.133353</v>
+        <v>0.0025</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.042129</v>
+        <v>0.007988</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.024577</v>
+        <v>0.003577</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.065483</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.004595</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -21537,7 +21537,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">

--- a/output/pdf_financials_xlsx/BEAR.xlsx
+++ b/output/pdf_financials_xlsx/BEAR.xlsx
@@ -11950,7 +11950,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -13722,7 +13726,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
